--- a/mosip_master/xlsx/identity_schema.xlsx
+++ b/mosip_master/xlsx/identity_schema.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D48FB5-B25F-492B-8113-55CD93EF338F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C406CBD-8CD7-4E38-81BA-F4FB1082E030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,6 +193,37 @@
 					"fieldType": "default",
 					"$ref": "#/definitions/biometricsType"
 				},
+				"selectedHandles": {
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "array",
+					"items": {
+						"type": "string"
+					},
+					"fieldType": "default"
+				},
+				"handleIdType": {
+					"bioAttributes": [],
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"handleIdValue": {
+					"bioAttributes": [],
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default"
+				},
+				"nationalId": {
+					"bioAttributes": [],
+					"fieldCategory": "none",
+					"format": "none",
+					"type": "string",
+					"fieldType": "default",
+					"handle": true
+				},
 				"island": {
 					"bioAttributes": [],
 					"validators": [
@@ -338,6 +369,13 @@
 				"residenceStatus": {
 					"bioAttributes": [
 					],
+					"fieldCategory": "kyc",
+					"format": "none",
+					"fieldType": "default",
+					"$ref": "#\/definitions\/simpleType"
+				},
+				"placeOfBirth": {
+					"bioAttributes": [],
 					"fieldCategory": "kyc",
 					"format": "none",
 					"fieldType": "default",
@@ -467,7 +505,7 @@
 					"bioAttributes": [
 					],
 					"validators": [{
-						"validator": "^\\+239\\s?[0-9]{7}$",
+						"validator": "^\\+?[1-9][0-9]{7,14}$",
 						"arguments": [
 						],
 						"type": "regex"
